--- a/artfynd/A 46267-2023 artfynd.xlsx
+++ b/artfynd/A 46267-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46267-2023 artfynd.xlsx
+++ b/artfynd/A 46267-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75247189</v>
+        <v>113557467</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grönberget, höjd Ö om, Ång</t>
+          <t>Grönberget Rossön nv, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561531.0040754934</v>
+        <v>561508</v>
       </c>
       <c r="R2" t="n">
-        <v>7094142.196986001</v>
+        <v>7094132</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,48 +765,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>gammal granskog i östsluttning</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>4 substratenheter # granlågor av olika ålder</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>75247190</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,12 +801,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561541.9647016432</v>
+        <v>561542</v>
       </c>
       <c r="R3" t="n">
-        <v>7094144.170692808</v>
+        <v>7094144</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,19 +849,9 @@
           <t>2018-07-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-07-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,12 +898,7 @@
         <v>75247188</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561335.8209441778</v>
+        <v>561336</v>
       </c>
       <c r="R4" t="n">
-        <v>7094267.979243455</v>
+        <v>7094268</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1006,19 +963,9 @@
           <t>2018-07-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-07-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,15 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113557467</v>
+        <v>75247189</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,41 +1020,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Grönberget Rossön nv, Ång</t>
+          <t>Grönberget, höjd Ö om, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561508</v>
+        <v>561531</v>
       </c>
       <c r="R5" t="n">
-        <v>7094132</v>
+        <v>7094142</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,17 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2018-07-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,19 +1090,238 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>gammal granskog i östsluttning</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>4 substratenheter # granlågor av olika ålder</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>97362925</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92369</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>S Hållbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>561321</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7094244</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>97362921</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>S Hållbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>561367</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7094374</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bodum</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-06-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46267-2023 artfynd.xlsx
+++ b/artfynd/A 46267-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247190</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247188</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75247189</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362925</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362921</t>
         </is>
       </c>
     </row>
@@ -1322,8 +1352,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113557467</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>